--- a/artfynd/A 18811-2025 artfynd.xlsx
+++ b/artfynd/A 18811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136296750</v>
       </c>
       <c r="B2" t="n">
-        <v>58243</v>
+        <v>58244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136296751</v>
       </c>
       <c r="B3" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18811-2025 artfynd.xlsx
+++ b/artfynd/A 18811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136296750</v>
       </c>
       <c r="B2" t="n">
-        <v>58244</v>
+        <v>58249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136296751</v>
       </c>
       <c r="B3" t="n">
-        <v>58609</v>
+        <v>58614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18811-2025 artfynd.xlsx
+++ b/artfynd/A 18811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136296750</v>
       </c>
       <c r="B2" t="n">
-        <v>58249</v>
+        <v>58262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136296751</v>
       </c>
       <c r="B3" t="n">
-        <v>58614</v>
+        <v>58627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
